--- a/Valuaciones_USA/ADBE_score_ponderados.xlsx
+++ b/Valuaciones_USA/ADBE_score_ponderados.xlsx
@@ -1015,64 +1015,64 @@
         <v>2</v>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -2705,64 +2705,64 @@
         <v>100</v>
       </c>
       <c r="C34" t="n">
-        <v>63.25</v>
+        <v>61.25</v>
       </c>
       <c r="D34" t="n">
-        <v>52.5</v>
+        <v>50.5</v>
       </c>
       <c r="E34" t="n">
-        <v>67.25</v>
+        <v>65.25</v>
       </c>
       <c r="F34" t="n">
-        <v>85.25</v>
+        <v>83.25</v>
       </c>
       <c r="G34" t="n">
-        <v>53.75</v>
+        <v>51.75</v>
       </c>
       <c r="H34" t="n">
-        <v>73.75</v>
+        <v>71.75</v>
       </c>
       <c r="I34" t="n">
-        <v>73.75</v>
+        <v>71.75</v>
       </c>
       <c r="J34" t="n">
-        <v>61.25</v>
+        <v>59.25</v>
       </c>
       <c r="K34" t="n">
-        <v>39.75</v>
+        <v>37.75</v>
       </c>
       <c r="L34" t="n">
-        <v>42.25</v>
+        <v>40.25</v>
       </c>
       <c r="M34" t="n">
-        <v>39.5</v>
+        <v>37.5</v>
       </c>
       <c r="N34" t="n">
-        <v>70.5</v>
+        <v>68.5</v>
       </c>
       <c r="O34" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="P34" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>78</v>
+      </c>
+      <c r="R34" t="n">
+        <v>83</v>
+      </c>
+      <c r="S34" t="n">
         <v>79.5</v>
       </c>
-      <c r="Q34" t="n">
-        <v>80</v>
-      </c>
-      <c r="R34" t="n">
-        <v>85</v>
-      </c>
-      <c r="S34" t="n">
-        <v>81.5</v>
-      </c>
       <c r="T34" t="n">
-        <v>83.75</v>
+        <v>81.75</v>
       </c>
       <c r="U34" t="n">
-        <v>82.5</v>
+        <v>80.5</v>
       </c>
       <c r="V34" t="n">
-        <v>70.25</v>
+        <v>68.25</v>
       </c>
     </row>
   </sheetData>
